--- a/data/00981A_20260826.xlsx
+++ b/data/00981A_20260826.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="206">
   <si>
-    <t xml:space="preserve">資料日期：115/08/25</t>
+    <t xml:space="preserve">資料日期：115/08/26</t>
   </si>
   <si>
     <t xml:space="preserve">基金資產</t>
@@ -23,7 +23,7 @@
     <t xml:space="preserve">淨資產</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 282,667,869,984</t>
+    <t xml:space="preserve">NTD 289,907,507,432</t>
   </si>
   <si>
     <t xml:space="preserve">流通在外單位數</t>
@@ -35,7 +35,7 @@
     <t xml:space="preserve">每單位淨值</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 28.78</t>
+    <t xml:space="preserve">NTD 29.51</t>
   </si>
   <si>
     <t xml:space="preserve">項目</t>
@@ -50,43 +50,43 @@
     <t xml:space="preserve">期貨(名目本金)</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 6,115,345,600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16%</t>
+    <t xml:space="preserve">NTD 6,247,207,400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15%</t>
   </si>
   <si>
     <t xml:space="preserve">股票</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 273,464,783,025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.74%</t>
+    <t xml:space="preserve">NTD 281,238,676,290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.01%</t>
   </si>
   <si>
     <t xml:space="preserve">現金</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 4,381,213,268</t>
+    <t xml:space="preserve">NTD 3,227,005,493</t>
   </si>
   <si>
     <t xml:space="preserve">期貨保證金</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 1,747,215,338</t>
+    <t xml:space="preserve">NTD 1,879,077,138</t>
   </si>
   <si>
     <t xml:space="preserve">附買回債券</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD 2,121,007,873</t>
+    <t xml:space="preserve">NTD 3,031,007,873</t>
   </si>
   <si>
     <t xml:space="preserve">應收付證券款</t>
   </si>
   <si>
-    <t xml:space="preserve">NTD -763,485,754</t>
+    <t xml:space="preserve">NTD -657,396,740</t>
   </si>
   <si>
     <t xml:space="preserve">期貨代號</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">11,884,000</t>
   </si>
   <si>
-    <t xml:space="preserve">10.09%</t>
+    <t xml:space="preserve">9.90%</t>
   </si>
   <si>
     <t xml:space="preserve">2383</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">4,843,000</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59%</t>
+    <t xml:space="preserve">9.85%</t>
   </si>
   <si>
     <t xml:space="preserve">3037</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">20,300,000</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86%</t>
+    <t xml:space="preserve">8.12%</t>
   </si>
   <si>
     <t xml:space="preserve">2454</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">5,148,000</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80%</t>
+    <t xml:space="preserve">7.01%</t>
   </si>
   <si>
     <t xml:space="preserve">3017</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">奇鋐</t>
   </si>
   <si>
-    <t xml:space="preserve">5,899,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16%</t>
+    <t xml:space="preserve">5,979,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51%</t>
   </si>
   <si>
     <t xml:space="preserve">6669</t>
@@ -194,7 +194,43 @@
     <t xml:space="preserve">2,226,000</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07%</t>
+    <t xml:space="preserve">5.21%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">健策</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,407,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">國巨*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25,387,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">智邦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,564,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65%</t>
   </si>
   <si>
     <t xml:space="preserve">6223</t>
@@ -206,43 +242,7 @@
     <t xml:space="preserve">2,486,000</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">國巨*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25,387,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">智邦</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,564,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">健策</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,407,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43%</t>
+    <t xml:space="preserve">4.32%</t>
   </si>
   <si>
     <t xml:space="preserve">2308</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">7,040,000</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26%</t>
+    <t xml:space="preserve">4.25%</t>
   </si>
   <si>
     <t xml:space="preserve">3711</t>
@@ -266,7 +266,19 @@
     <t xml:space="preserve">19,479,000</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07%</t>
+    <t xml:space="preserve">3.98%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南電</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9,624,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92%</t>
   </si>
   <si>
     <t xml:space="preserve">2303</t>
@@ -278,19 +290,7 @@
     <t xml:space="preserve">89,518,000</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">南電</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9,624,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95%</t>
+    <t xml:space="preserve">3.81%</t>
   </si>
   <si>
     <t xml:space="preserve">3665</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">4,671,848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43%</t>
+    <t xml:space="preserve">3.23%</t>
   </si>
   <si>
     <t xml:space="preserve">6274</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">5,498,000</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89%</t>
+    <t xml:space="preserve">2.90%</t>
   </si>
   <si>
     <t xml:space="preserve">5274</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">383,900</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09%</t>
+    <t xml:space="preserve">2.08%</t>
   </si>
   <si>
     <t xml:space="preserve">6805</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">2,264,000</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48%</t>
+    <t xml:space="preserve">1.58%</t>
   </si>
   <si>
     <t xml:space="preserve">2449</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">11,275,450</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96%</t>
+    <t xml:space="preserve">0.95%</t>
   </si>
   <si>
     <t xml:space="preserve">8210</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">2,477,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.85%</t>
+    <t xml:space="preserve">0.83%</t>
   </si>
   <si>
     <t xml:space="preserve">2368</t>
@@ -374,7 +374,19 @@
     <t xml:space="preserve">1,957,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.67%</t>
+    <t xml:space="preserve">0.70%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">創意</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.69%</t>
   </si>
   <si>
     <t xml:space="preserve">8996</t>
@@ -386,7 +398,7 @@
     <t xml:space="preserve">1,301,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.56%</t>
+    <t xml:space="preserve">0.54%</t>
   </si>
   <si>
     <t xml:space="preserve">4979</t>
@@ -398,18 +410,6 @@
     <t xml:space="preserve">2,424,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">創意</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255,000</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.50%</t>
   </si>
   <si>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">5,917,000</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45%</t>
+    <t xml:space="preserve">0.44%</t>
   </si>
   <si>
     <t xml:space="preserve">6510</t>
@@ -434,6 +434,9 @@
     <t xml:space="preserve">477,000</t>
   </si>
   <si>
+    <t xml:space="preserve">0.43%</t>
+  </si>
+  <si>
     <t xml:space="preserve">4958</t>
   </si>
   <si>
@@ -446,6 +449,18 @@
     <t xml:space="preserve">0.26%</t>
   </si>
   <si>
+    <t xml:space="preserve">6278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">台表科</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,249,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.22%</t>
+  </si>
+  <si>
     <t xml:space="preserve">6187</t>
   </si>
   <si>
@@ -453,21 +468,6 @@
   </si>
   <si>
     <t xml:space="preserve">483,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.22%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">台表科</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,249,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21%</t>
   </si>
   <si>
     <t xml:space="preserve">6271</t>
@@ -1424,7 +1424,8 @@
   <dimension ref="A1:F73"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="24.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.35" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.05" bestFit="1" customWidth="1"/>
@@ -1973,49 +1974,49 @@
         <v>139</v>
       </c>
       <c r="D49" s="139" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="140" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B50" s="141" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C50" s="142" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D50" s="143" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="144" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B51" s="145" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C51" s="146" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D51" s="147" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="148" t="s">
+        <v>149</v>
+      </c>
+      <c r="B52" s="149" t="s">
+        <v>150</v>
+      </c>
+      <c r="C52" s="150" t="s">
+        <v>151</v>
+      </c>
+      <c r="D52" s="151" t="s">
         <v>148</v>
-      </c>
-      <c r="B52" s="149" t="s">
-        <v>149</v>
-      </c>
-      <c r="C52" s="150" t="s">
-        <v>150</v>
-      </c>
-      <c r="D52" s="151" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="53">
